--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487524_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487524_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.6272</v>
+        <v>7.4086</v>
       </c>
       <c r="E2" t="n">
-        <v>10.7557</v>
+        <v>7.0716</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8716</v>
+        <v>0.3369</v>
       </c>
       <c r="G2" t="n">
         <v>1.9743</v>
@@ -610,13 +610,13 @@
         <v>3.5253</v>
       </c>
       <c r="S2" t="n">
-        <v>6.0696</v>
+        <v>1.8509</v>
       </c>
       <c r="T2" t="n">
-        <v>5.5749</v>
+        <v>1.8908</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4946</v>
+        <v>-0.04</v>
       </c>
       <c r="V2" t="n">
         <v>1.0374</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7359</v>
+        <v>2.844</v>
       </c>
       <c r="E3" t="n">
-        <v>2.666</v>
+        <v>3.587</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9301</v>
+        <v>-0.743</v>
       </c>
       <c r="G3" t="n">
         <v>3.0861</v>
@@ -688,13 +688,13 @@
         <v>2.1543</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4244</v>
+        <v>-0.3163</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.891</v>
+        <v>0.03</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5334</v>
+        <v>-0.3463</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1217</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8391</v>
+        <v>0.9903</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3274</v>
+        <v>1.5321</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4883</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>0.3077</v>
@@ -766,13 +766,13 @@
         <v>0.5875</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0655</v>
+        <v>0.2167</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0594</v>
+        <v>0.1453</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1249</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1217</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MIRANDA GARCIA</t>
+          <t>N. LOPEZ ALVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6583</v>
+        <v>0.9727</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1773</v>
+        <v>1.6284</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5191</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0725</v>
+        <v>-0.1679</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1837</v>
+        <v>-0.476</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1112</v>
+        <v>0.3081</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6878</v>
+        <v>1.3872</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0412</v>
+        <v>0.8166</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6466</v>
+        <v>0.5706</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7603</v>
+        <v>-1.5551</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2249</v>
+        <v>-1.2926</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5354</v>
+        <v>-0.2625</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3917</v>
+        <v>0.7834</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3917</v>
+        <v>0.7834</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0061</v>
+        <v>0.3571</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1188</v>
+        <v>0.2411</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1249</v>
+        <v>0.116</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3329</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6083</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. LOPEZ ALVAREZ-TIRADOR</t>
+          <t>A. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.283</v>
+        <v>0.8095</v>
       </c>
       <c r="E6" t="n">
-        <v>0.912</v>
+        <v>2.382</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.629</v>
+        <v>-1.5725</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1679</v>
+        <v>-0.0725</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.476</v>
+        <v>-0.1837</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3081</v>
+        <v>0.1112</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3872</v>
+        <v>1.6878</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8166</v>
+        <v>1.0412</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5706</v>
+        <v>0.6466</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5551</v>
+        <v>-1.7603</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2926</v>
+        <v>-1.2249</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2625</v>
+        <v>-0.5354</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7834</v>
+        <v>0.3917</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7834</v>
+        <v>0.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3325</v>
+        <v>0.1573</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4752</v>
+        <v>0.0859</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1427</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6083</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0808</v>
+        <v>-0.4309</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2154</v>
+        <v>0.1939</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8653999999999999</v>
+        <v>-0.6249</v>
       </c>
       <c r="G7" t="n">
         <v>1.508</v>
@@ -1000,13 +1000,13 @@
         <v>1.7626</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.567</v>
+        <v>-0.9171</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7722</v>
+        <v>-0.3629</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7947</v>
+        <v>-0.5542</v>
       </c>
       <c r="V7" t="n">
         <v>-0.8260999999999999</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8434</v>
+        <v>-1.5991</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8385</v>
+        <v>-1.3268</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.005</v>
+        <v>-0.2723</v>
       </c>
       <c r="G8" t="n">
         <v>-1.4668</v>
@@ -1078,13 +1078,13 @@
         <v>2.1543</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2135</v>
+        <v>0.0309</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2682</v>
+        <v>0.2435</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0547</v>
+        <v>-0.2126</v>
       </c>
       <c r="V8" t="n">
         <v>-1.3383</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9555</v>
+        <v>-1.7463</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3638</v>
+        <v>-0.2614</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5918</v>
+        <v>-1.4848</v>
       </c>
       <c r="G9" t="n">
         <v>-0.6924</v>
@@ -1156,13 +1156,13 @@
         <v>0.5875</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.3488</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3564</v>
+        <v>-0.2541</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2016</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>0.6659</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9647</v>
+        <v>-2.7867</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3541</v>
+        <v>-0.1494</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6106</v>
+        <v>-2.6373</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6794</v>
@@ -1234,13 +1234,13 @@
         <v>2.7419</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1013</v>
+        <v>0.0766</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2682</v>
+        <v>-0.0635</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1669</v>
+        <v>0.1401</v>
       </c>
       <c r="V10" t="n">
         <v>-1.9466</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. ARIAS GONZALEZ</t>
+          <t>. SUAREZ HEVIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5961</v>
+        <v>-3.021</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7558</v>
+        <v>-2.3884</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.3519</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8507</v>
+        <v>-1.2229</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8051</v>
+        <v>0.2116</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0456</v>
+        <v>-1.4346</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7127</v>
+        <v>1.1343</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7791</v>
+        <v>1.7761</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0664</v>
+        <v>-0.6418</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.5634</v>
+        <v>-2.3572</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.5842</v>
+        <v>-1.5645</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0208</v>
+        <v>-0.7927</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9585</v>
+        <v>-3.917</v>
       </c>
       <c r="R11" t="n">
         <v>1.9585</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6878</v>
+        <v>-0.3327</v>
       </c>
       <c r="T11" t="n">
-        <v>1.3933</v>
+        <v>-0.0988</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7055</v>
+        <v>-0.2339</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4332</v>
+        <v>0.4931</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6083</v>
+        <v>0.4931</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.0415</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>. SUAREZ HEVIA</t>
+          <t>R. FERNANDEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8221</v>
+        <v>-3.4718</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0024</v>
+        <v>-2.3935</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8197</v>
+        <v>-1.0784</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.2229</v>
+        <v>-1.7599</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2116</v>
+        <v>0.8778</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.4346</v>
+        <v>-2.6377</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1343</v>
+        <v>-0.6974</v>
       </c>
       <c r="K12" t="n">
-        <v>1.7761</v>
+        <v>1.4205</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6418</v>
+        <v>-2.1179</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.3572</v>
+        <v>-1.0625</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5645</v>
+        <v>-0.5427</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7927</v>
+        <v>-0.5198</v>
       </c>
       <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>-1.9585</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-3.917</v>
       </c>
       <c r="R12" t="n">
         <v>1.9585</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1339</v>
+        <v>-0.22</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7128</v>
+        <v>-0.0129</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.421</v>
+        <v>-0.207</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4931</v>
+        <v>-1.492</v>
       </c>
       <c r="W12" t="n">
-        <v>0.4931</v>
+        <v>0.2754</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.7673</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ FERNANDEZ</t>
+          <t>J. ARIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,40 +1423,40 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.3974</v>
+        <v>-4.4858</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.2121</v>
+        <v>-0.2675</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1853</v>
+        <v>-4.2182</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.7599</v>
+        <v>-1.8507</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8778</v>
+        <v>-1.8051</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.6377</v>
+        <v>-0.0456</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6974</v>
+        <v>0.7127</v>
       </c>
       <c r="K13" t="n">
-        <v>1.4205</v>
+        <v>0.7791</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.1179</v>
+        <v>-0.0664</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.0625</v>
+        <v>-2.5634</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5427</v>
+        <v>-2.5842</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5198</v>
+        <v>0.0208</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1468,22 +1468,22 @@
         <v>1.9585</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1456</v>
+        <v>-0.2019</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8316</v>
+        <v>0.3699</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3139</v>
+        <v>-0.5718</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.492</v>
+        <v>-2.4332</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2754</v>
+        <v>0.6083</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.7673</v>
+        <v>-3.0415</v>
       </c>
     </row>
     <row r="14">
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.516500000000002</v>
+        <v>-4.516500000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>9.607900000000001</v>
+        <v>9.607999999999999</v>
       </c>
       <c r="F14" t="n">
         <v>-14.1246</v>
@@ -1513,7 +1513,7 @@
         <v>-3.0364</v>
       </c>
       <c r="H14" t="n">
-        <v>1.005</v>
+        <v>1.005000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>-4.041600000000001</v>
@@ -1525,7 +1525,7 @@
         <v>19.7017</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1816999999999998</v>
+        <v>-0.1817</v>
       </c>
       <c r="M14" t="n">
         <v>-22.5564</v>
@@ -1546,16 +1546,16 @@
         <v>20.564</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3528</v>
+        <v>0.3527</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2144</v>
+        <v>2.2143</v>
       </c>
       <c r="U14" t="n">
         <v>-1.8614</v>
       </c>
       <c r="V14" t="n">
-        <v>-5.7503</v>
+        <v>-5.750299999999999</v>
       </c>
       <c r="W14" t="n">
         <v>4.520899999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.5669</v>
+        <v>9.815799999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>9.9597</v>
+        <v>10.369</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3928</v>
+        <v>-0.5532</v>
       </c>
       <c r="G15" t="n">
         <v>5.9066</v>
@@ -1624,13 +1624,13 @@
         <v>2.7419</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2304</v>
+        <v>0.0185</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2682</v>
+        <v>0.1411</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0378</v>
+        <v>-0.1226</v>
       </c>
       <c r="V15" t="n">
         <v>7.0243</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7881</v>
+        <v>1.7484</v>
       </c>
       <c r="E16" t="n">
-        <v>3.78</v>
+        <v>3.473</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.992</v>
+        <v>-1.7247</v>
       </c>
       <c r="G16" t="n">
         <v>0.9922</v>
@@ -1702,13 +1702,13 @@
         <v>1.7626</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3258</v>
+        <v>0.2861</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8299</v>
+        <v>0.5228</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.504</v>
+        <v>-0.2367</v>
       </c>
       <c r="V16" t="n">
         <v>0.6659</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0581</v>
+        <v>0.7605</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4846</v>
+        <v>2.3032</v>
       </c>
       <c r="F17" t="n">
         <v>-1.5427</v>
@@ -1780,10 +1780,10 @@
         <v>2.546</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2216</v>
+        <v>-0.4029</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7722</v>
+        <v>0.0465</v>
       </c>
       <c r="U17" t="n">
         <v>-0.4493</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. GARCIA FRAGA</t>
+          <t>L. SANCHEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1021</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5888</v>
+        <v>1.764</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6909</v>
+        <v>-1.7013</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7706</v>
+        <v>0.0598</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0483</v>
+        <v>-0.6372</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7223000000000001</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8481</v>
+        <v>2.3483</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7672</v>
+        <v>1.8084</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0808</v>
+        <v>0.5399</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6187</v>
+        <v>-2.2884</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8156</v>
+        <v>-2.4456</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8031</v>
+        <v>0.1572</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1751</v>
+        <v>1.9585</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4151</v>
+        <v>-0.663</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4446</v>
+        <v>0.1576</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0295</v>
+        <v>-0.8206</v>
       </c>
       <c r="V18" t="n">
-        <v>0.0576</v>
+        <v>0.6659</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2754</v>
+        <v>1.2166</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2178</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. SABATER MARTINEZ</t>
+          <t>M. GARCIA FRAGA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1591</v>
+        <v>-0.351</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2021</v>
+        <v>0.1795</v>
       </c>
       <c r="F19" t="n">
-        <v>1.043</v>
+        <v>-0.5305</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8022</v>
+        <v>-0.7706</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.014</v>
+        <v>-0.0483</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7883</v>
+        <v>-0.7223000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5998</v>
+        <v>0.8481</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9546</v>
+        <v>0.7672</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3548</v>
+        <v>0.0808</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4021</v>
+        <v>-1.6187</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9686</v>
+        <v>-0.8156</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5666</v>
+        <v>-0.8031</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3709</v>
+        <v>0.1958</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.917</v>
+        <v>-0.9792</v>
       </c>
       <c r="R19" t="n">
-        <v>2.546</v>
+        <v>1.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>2.0717</v>
+        <v>0.1661</v>
       </c>
       <c r="T19" t="n">
-        <v>1.8973</v>
+        <v>0.0353</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1744</v>
+        <v>0.1309</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0576</v>
+        <v>0.0576</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2178</v>
+        <v>0.2754</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2754</v>
+        <v>-0.2178</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. SANCHEZ VAZQUEZ</t>
+          <t>I. LUACES PENIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3779</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>1.457</v>
+        <v>1.0344</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8349</v>
+        <v>-1.8424</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0598</v>
+        <v>-0.2263</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6372</v>
+        <v>-0.2214</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6971000000000001</v>
+        <v>-0.0048</v>
       </c>
       <c r="J20" t="n">
-        <v>2.3483</v>
+        <v>1.256</v>
       </c>
       <c r="K20" t="n">
-        <v>1.8084</v>
+        <v>1.8169</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5399</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2884</v>
+        <v>-1.4822</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.4456</v>
+        <v>-2.0384</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1572</v>
+        <v>0.5562</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.1958</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9585</v>
+        <v>1.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1036</v>
+        <v>-0.4446</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1494</v>
+        <v>0.207</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9542</v>
+        <v>-0.6516</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6659</v>
+        <v>-0.3329</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2166</v>
+        <v>0.5507</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5507</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6108</v>
+        <v>-0.8246</v>
       </c>
       <c r="E21" t="n">
         <v>-0.0337</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.7909</v>
       </c>
       <c r="G21" t="n">
         <v>0.8397</v>
@@ -2092,13 +2092,13 @@
         <v>1.9585</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3744</v>
+        <v>0.1606</v>
       </c>
       <c r="T21" t="n">
         <v>0.1476</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2268</v>
+        <v>0.0129</v>
       </c>
       <c r="V21" t="n">
         <v>-1.8249</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. LUACES PENIN</t>
+          <t>A. SOTO MARTINEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7010999999999999</v>
+        <v>-0.8656</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0344</v>
+        <v>-0.039</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7355</v>
+        <v>-0.8267</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2263</v>
+        <v>-0.9223</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2214</v>
+        <v>-0.2504</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0048</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>1.256</v>
+        <v>0.0204</v>
       </c>
       <c r="K22" t="n">
-        <v>1.8169</v>
+        <v>0.0204</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5610000000000001</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4822</v>
+        <v>-0.9427</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.0384</v>
+        <v>-0.2708</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5562</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1751</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3377</v>
+        <v>0.0566</v>
       </c>
       <c r="T22" t="n">
-        <v>0.207</v>
+        <v>-0.0594</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5447</v>
+        <v>0.116</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5507</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. SOTO MARTINEZ</t>
+          <t>G. SABATER MARTINEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8389</v>
+        <v>-1.8904</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.039</v>
+        <v>-2.5324</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7999000000000001</v>
+        <v>0.6421</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9223</v>
+        <v>-0.8022</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2504</v>
+        <v>-0.014</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.7883</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0204</v>
+        <v>0.5998</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0204</v>
+        <v>1.9546</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-1.3548</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9427</v>
+        <v>-1.4021</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2708</v>
+        <v>-1.9686</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6719000000000001</v>
+        <v>0.5666</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-3.917</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.546</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0833</v>
+        <v>0.3404</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0594</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1427</v>
+        <v>-0.2266</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.0576</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2178</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9904</v>
+        <v>-3.1313</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9052</v>
+        <v>-2.3936</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0852</v>
+        <v>-0.7377</v>
       </c>
       <c r="G24" t="n">
         <v>-1.5151</v>
@@ -2326,13 +2326,13 @@
         <v>0.7834</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7299</v>
+        <v>0.1292</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4158</v>
+        <v>0.0959</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3141</v>
+        <v>0.0334</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5495</v>
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>4.5166</v>
+        <v>4.516500000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>14.1245</v>
+        <v>14.1244</v>
       </c>
       <c r="F25" t="n">
         <v>-9.608000000000001</v>
@@ -2383,7 +2383,7 @@
         <v>18.6965</v>
       </c>
       <c r="L25" t="n">
-        <v>3.859800000000001</v>
+        <v>3.8598</v>
       </c>
       <c r="M25" t="n">
         <v>-19.5201</v>
@@ -2392,10 +2392,10 @@
         <v>-19.7017</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1817000000000003</v>
+        <v>0.1817</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.917</v>
+        <v>-3.917000000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>-20.5641</v>
@@ -2404,13 +2404,13 @@
         <v>16.6471</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3529000000000002</v>
+        <v>-0.353</v>
       </c>
       <c r="T25" t="n">
         <v>1.8614</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.2141</v>
+        <v>-2.2142</v>
       </c>
       <c r="V25" t="n">
         <v>5.7502</v>
